--- a/input/Studies/MEET2/AllEquipment.xlsx
+++ b/input/Studies/MEET2/AllEquipment.xlsx
@@ -913,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:BC2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1213,6 +1213,21 @@
           <t>Factor Tag</t>
         </is>
       </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>CCEE Ratio Distribution</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>Compressor Efficiency</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>Crankcase Emissions Flag</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1394,6 +1409,15 @@
         <is>
           <t>wellpad_compressor_above500HP</t>
         </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BC2" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1618,7 +1642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:BC2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1917,6 +1941,21 @@
           <t>Exhaust Factors</t>
         </is>
       </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>CCEE Ratio Distribution</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>Compressor Efficiency</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>Crankcase Emissions Flag</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2098,6 +2137,15 @@
         <is>
           <t>DestEff</t>
         </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BC2" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5919,7 +5967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5942,39 +5990,79 @@
           <t>Unit ID</t>
         </is>
       </c>
-      <c r="C1" s="36" t="inlineStr">
-        <is>
-          <t>Component Leak Survey Frequency [days]</t>
-        </is>
-      </c>
-      <c r="D1" s="36" t="inlineStr">
-        <is>
-          <t>Component Count</t>
-        </is>
-      </c>
-      <c r="E1" s="36" t="inlineStr">
-        <is>
-          <t>Component pLeak</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Actuator Type [Gas, Electric, Air]</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Model ID</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Leak GC Name</t>
-        </is>
-      </c>
-      <c r="I1" s="7" t="inlineStr">
-        <is>
-          <t>Factor Tag</t>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Flash Tank</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Glycol Pump</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Glycol Pump Injection Ratio</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Glycol Type</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Lean Glycol Circulation Rate</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Lean Glycol Circulation Ratio</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Operating Hours</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Still Vent Controlled Flag</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Stripping Gas Flow Rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Tank Flash Controlled Flag</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Wet Gas Flow Rate</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Wet Gas Pressure</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Wet Gas Temperature</t>
         </is>
       </c>
     </row>
@@ -5989,34 +6077,58 @@
           <t>dehy_1</t>
         </is>
       </c>
-      <c r="C2" s="6" t="n">
-        <v>365</v>
-      </c>
-      <c r="D2" s="37" t="n">
-        <v>182</v>
-      </c>
-      <c r="E2" s="37" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Gas</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Dehydrator.json</t>
         </is>
       </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Gas Assisted</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>4.5</v>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Default-LeakGc</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>ts_dehy</t>
-        </is>
+          <t>TEG</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8760</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>957</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>92.40000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/input/Studies/MEET2/AllEquipment.xlsx
+++ b/input/Studies/MEET2/AllEquipment.xlsx
@@ -5967,7 +5967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5992,75 +5992,70 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Actuator Type [Gas, Electric, Air]</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
           <t>Model ID</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Flash Tank</t>
+        </is>
+      </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Flash Tank</t>
+          <t>Glycol Pump</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Glycol Pump</t>
+          <t>Glycol Pump Injection Ratio</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Glycol Pump Injection Ratio</t>
+          <t>Glycol Type</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Glycol Type</t>
+          <t>Lean Glycol Circulation Rate</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Lean Glycol Circulation Rate</t>
+          <t>Lean Glycol Circulation Ratio</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Lean Glycol Circulation Ratio</t>
+          <t>Operating Hours</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Operating Hours</t>
+          <t>Still Vent Controlled Flag</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Still Vent Controlled Flag</t>
+          <t>Stripping Gas Flow Rate</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Stripping Gas Flow Rate</t>
+          <t>Tank Flash Controlled Flag</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Tank Flash Controlled Flag</t>
+          <t>Wet Gas Flow Rate</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Wet Gas Flow Rate</t>
+          <t>Wet Gas Pressure</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
-        <is>
-          <t>Wet Gas Pressure</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
         <is>
           <t>Wet Gas Temperature</t>
         </is>
@@ -6077,57 +6072,52 @@
           <t>dehy_1</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Gas</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Dehydrator.json</t>
         </is>
       </c>
-      <c r="E2" t="b">
+      <c r="D2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Gas Assisted</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="F2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>TEG</t>
         </is>
       </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
       <c r="I2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8760</v>
+      </c>
+      <c r="K2" t="b">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K2" t="n">
-        <v>8760</v>
-      </c>
-      <c r="L2" t="b">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" t="b">
         <v>0</v>
       </c>
-      <c r="N2" t="b">
-        <v>0</v>
+      <c r="N2" t="n">
+        <v>100000</v>
       </c>
       <c r="O2" t="n">
-        <v>100000</v>
+        <v>957</v>
       </c>
       <c r="P2" t="n">
-        <v>957</v>
-      </c>
-      <c r="Q2" t="n">
         <v>92.40000000000001</v>
       </c>
     </row>
